--- a/oec-ascend/oec/resource/base_report.xlsx
+++ b/oec-ascend/oec/resource/base_report.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>兼容性工具测试报告</t>
   </si>
@@ -72,6 +72,21 @@
     <t>结论</t>
   </si>
   <si>
+    <t>运行环境</t>
+  </si>
+  <si>
+    <t>环境信息</t>
+  </si>
+  <si>
+    <t>运行依赖</t>
+  </si>
+  <si>
+    <t>CANN安装</t>
+  </si>
+  <si>
+    <t>CANN卸载</t>
+  </si>
+  <si>
     <t>应用开发</t>
   </si>
   <si>
@@ -79,6 +94,9 @@
   </si>
   <si>
     <t>常用基础功能测试</t>
+  </si>
+  <si>
+    <t>算子加速库</t>
   </si>
   <si>
     <t>媒体处理</t>
@@ -486,7 +504,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -504,6 +522,43 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -633,7 +688,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -645,34 +700,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -757,7 +812,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -776,7 +831,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1304,7 +1368,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.6666666666667" customWidth="1"/>
@@ -1398,107 +1462,155 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="25" customHeight="1" spans="1:5">
+    <row r="10" ht="24" customHeight="1" spans="1:5">
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:5">
+      <c r="A11" s="8"/>
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" ht="25" customHeight="1" spans="1:5">
-      <c r="A11" s="6"/>
-      <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" ht="25" customHeight="1" spans="1:5">
-      <c r="A12" s="6" t="s">
-        <v>19</v>
-      </c>
+    <row r="12" ht="24" customHeight="1" spans="1:5">
+      <c r="A12" s="8"/>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" ht="25" customHeight="1" spans="1:5">
-      <c r="A13" s="6"/>
+    <row r="13" ht="24" customHeight="1" spans="1:5">
+      <c r="A13" s="9"/>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" ht="25" customHeight="1" spans="1:5">
-      <c r="A14" s="6" t="s">
-        <v>22</v>
+    <row r="14" ht="24" customHeight="1" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" ht="25" customHeight="1" spans="1:5">
-      <c r="A15" s="6"/>
+    <row r="15" ht="24" customHeight="1" spans="1:5">
+      <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" ht="25" customHeight="1" spans="1:5">
-      <c r="A16" s="6"/>
+    <row r="16" ht="24" customHeight="1" spans="1:5">
+      <c r="A16" s="3"/>
       <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" ht="25" customHeight="1" spans="1:5">
-      <c r="A17" s="6" t="s">
+    <row r="17" ht="24" customHeight="1" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" ht="25" customHeight="1" spans="1:5">
-      <c r="A18" s="6"/>
+    <row r="18" ht="24" customHeight="1" spans="1:5">
+      <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
     </row>
+    <row r="19" ht="24" customHeight="1" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:5">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:5">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:5">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A10:A13"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="A3:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1527,10 +1639,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>

--- a/oec-ascend/oec/resource/base_report.xlsx
+++ b/oec-ascend/oec/resource/base_report.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>兼容性工具测试报告</t>
   </si>
@@ -78,15 +78,33 @@
     <t>环境信息</t>
   </si>
   <si>
+    <t>读取操作系统、驱动信息</t>
+  </si>
+  <si>
+    <t>CANN信息</t>
+  </si>
+  <si>
+    <t>读取CANN版本、查询NPU信息</t>
+  </si>
+  <si>
     <t>运行依赖</t>
   </si>
   <si>
+    <t>检查系统库，pipy库依赖</t>
+  </si>
+  <si>
     <t>CANN安装</t>
   </si>
   <si>
+    <t>安装昇腾软件</t>
+  </si>
+  <si>
     <t>CANN卸载</t>
   </si>
   <si>
+    <t>卸载昇腾软件</t>
+  </si>
+  <si>
     <t>应用开发</t>
   </si>
   <si>
@@ -99,10 +117,13 @@
     <t>算子加速库</t>
   </si>
   <si>
+    <t>aclnn算子加速库接口测试</t>
+  </si>
+  <si>
     <t>媒体处理</t>
   </si>
   <si>
-    <t>多媒体</t>
+    <t>图像处理、视频编解码测试</t>
   </si>
   <si>
     <t>算子</t>
@@ -120,16 +141,28 @@
     <t>模型编译</t>
   </si>
   <si>
+    <t>模型编译工具基础能力测试</t>
+  </si>
+  <si>
     <t>模型调优</t>
   </si>
   <si>
+    <t>模型调优工具基础能力测试</t>
+  </si>
+  <si>
     <t>集合通信</t>
   </si>
   <si>
+    <t>集合通信基础能力测试</t>
+  </si>
+  <si>
     <t>集成测试</t>
   </si>
   <si>
     <t>离线推理</t>
+  </si>
+  <si>
+    <t>小模型离线推理能力测试</t>
   </si>
   <si>
     <t>在线训练</t>
@@ -151,7 +184,26 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,7 +365,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor rgb="FFE3F2D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -504,11 +556,54 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC6C6C6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC6C6C6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -520,32 +615,19 @@
         <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -553,14 +635,14 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,34 +746,20 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -700,147 +768,173 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -895,221 +989,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1119,9 +999,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1153,15 +1033,15 @@
         <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1231,132 +1111,167 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1367,289 +1282,329 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="16.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="26.7777777777778" customWidth="1"/>
-    <col min="4" max="4" width="28.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="34.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="16.7222222222222" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.4351851851852" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.1481481481481" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.287037037037" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4" t="s">
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4" t="s">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:5">
-      <c r="A10" s="6" t="s">
+    <row r="10" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:5">
+    <row r="11" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
       <c r="A11" s="8"/>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:5">
-      <c r="A12" s="8"/>
-      <c r="B12" s="4" t="s">
+      <c r="B11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:5">
-      <c r="A13" s="9"/>
-      <c r="B13" s="4" t="s">
+      <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:5">
-      <c r="A14" s="3" t="s">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A12" s="14"/>
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A13" s="14"/>
+      <c r="B13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:5">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4" t="s">
+      <c r="C13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:5">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A14" s="15"/>
+      <c r="B14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:5">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:5">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4" t="s">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:5">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4" t="s">
+      <c r="C17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:5">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="A3:C7"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.7777777777778" customWidth="1"/>
-    <col min="2" max="2" width="26.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="88.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="12.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="21.7222222222222" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.287037037037" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="88.7222222222222" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5740740740741" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="18.75" customHeight="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/oec-ascend/oec/resource/base_report.xlsx
+++ b/oec-ascend/oec/resource/base_report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="30720" windowHeight="12900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>兼容性工具测试报告</t>
   </si>
@@ -93,16 +93,10 @@
     <t>检查系统库，pipy库依赖</t>
   </si>
   <si>
-    <t>CANN安装</t>
-  </si>
-  <si>
-    <t>安装昇腾软件</t>
-  </si>
-  <si>
-    <t>CANN卸载</t>
-  </si>
-  <si>
-    <t>卸载昇腾软件</t>
+    <t>CANN安装卸载</t>
+  </si>
+  <si>
+    <t>安装卸载toolkit,kernels,nnal软件</t>
   </si>
   <si>
     <t>应用开发</t>
@@ -900,7 +894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -935,15 +929,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1299,7 +1284,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.7222222222222" style="4" customWidth="1"/>
@@ -1443,24 +1428,24 @@
       <c r="E13" s="7"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A14" s="14"/>
+      <c r="A14" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="B14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="11" t="s">
         <v>24</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A15" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="7"/>
@@ -1478,20 +1463,20 @@
       <c r="E16" s="7"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>30</v>
       </c>
+      <c r="B17" s="11" t="s">
+        <v>31</v>
+      </c>
       <c r="C17" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="11" t="s">
         <v>33</v>
       </c>
@@ -1502,20 +1487,20 @@
       <c r="E18" s="7"/>
     </row>
     <row r="19" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A19" s="6"/>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>35</v>
       </c>
+      <c r="B19" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="C19" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
     </row>
     <row r="20" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>38</v>
       </c>
@@ -1537,20 +1522,20 @@
       <c r="E21" s="7"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A22" s="6"/>
+      <c r="A22" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="B22" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A23" s="15" t="s">
-        <v>44</v>
-      </c>
+      <c r="A23" s="13"/>
       <c r="B23" s="7" t="s">
         <v>45</v>
       </c>
@@ -1561,7 +1546,7 @@
       <c r="E23" s="7"/>
     </row>
     <row r="24" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A24" s="16"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="7" t="s">
         <v>47</v>
       </c>
@@ -1570,27 +1555,16 @@
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-    </row>
-    <row r="25" s="3" customFormat="1" ht="24" customHeight="1" spans="1:5">
-      <c r="A25" s="17"/>
-      <c r="B25" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A3:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1621,10 +1595,10 @@
         <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>13</v>
